--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,18 +410,21 @@
         <v>qty</v>
       </c>
       <c r="D1" t="str">
+        <v>divQty</v>
+      </c>
+      <c r="E1" t="str">
         <v>avgPrice</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>currentPrice</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>dividend</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>netDividend</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>sector</v>
       </c>
     </row>
@@ -433,21 +436,24 @@
         <v>Equity</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>456.15</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>462.6</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
         <v>Mining / PSU</v>
       </c>
     </row>
@@ -459,21 +465,24 @@
         <v>Equity</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <v>1380</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1620</v>
       </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
       <c r="G3">
-        <v>2700</v>
-      </c>
-      <c r="H3" t="str">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>94</v>
+      </c>
+      <c r="I3" t="str">
         <v>IT Services</v>
       </c>
     </row>
@@ -485,21 +494,24 @@
         <v>Equity</v>
       </c>
       <c r="C4">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>440</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>462</v>
       </c>
-      <c r="F4">
-        <v>13.75</v>
-      </c>
       <c r="G4">
-        <v>3712.5</v>
-      </c>
-      <c r="H4" t="str">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
         <v>FMCG / Diversified</v>
       </c>
     </row>
@@ -511,21 +523,24 @@
         <v>Equity</v>
       </c>
       <c r="C5">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>420</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>480</v>
       </c>
-      <c r="F5">
-        <v>18</v>
-      </c>
       <c r="G5">
-        <v>2430</v>
-      </c>
-      <c r="H5" t="str">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
         <v>NBFC / PSU</v>
       </c>
     </row>
@@ -537,21 +552,24 @@
         <v>Equity</v>
       </c>
       <c r="C6">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>520</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>590</v>
       </c>
-      <c r="F6">
-        <v>17</v>
-      </c>
       <c r="G6">
-        <v>2295</v>
-      </c>
-      <c r="H6" t="str">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
         <v>NBFC / PSU</v>
       </c>
     </row>
@@ -563,21 +581,24 @@
         <v>Equity</v>
       </c>
       <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>200</v>
       </c>
-      <c r="D7">
-        <v>200</v>
-      </c>
-      <c r="E7">
+      <c r="F7">
         <v>205</v>
       </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
       <c r="G7">
-        <v>1620</v>
-      </c>
-      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
         <v>Lubricants</v>
       </c>
     </row>
@@ -589,21 +610,24 @@
         <v>Equity</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>430</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>460</v>
       </c>
-      <c r="F8">
-        <v>50</v>
-      </c>
       <c r="G8">
-        <v>4500</v>
-      </c>
-      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
         <v>Mining / Metals</v>
       </c>
     </row>
@@ -615,21 +639,24 @@
         <v>REIT</v>
       </c>
       <c r="C9">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>135</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>140</v>
       </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
       <c r="G9">
-        <v>1620</v>
-      </c>
-      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
         <v>Retail REIT</v>
       </c>
     </row>
@@ -641,21 +668,24 @@
         <v>REIT</v>
       </c>
       <c r="C10">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>340</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>345</v>
       </c>
-      <c r="F10">
-        <v>21</v>
-      </c>
       <c r="G10">
-        <v>2835</v>
-      </c>
-      <c r="H10" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
         <v>Office REIT</v>
       </c>
     </row>
@@ -667,21 +697,24 @@
         <v>REIT</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>285</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>290</v>
       </c>
-      <c r="F11">
-        <v>22</v>
-      </c>
       <c r="G11">
-        <v>1980</v>
-      </c>
-      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
         <v>Office REIT</v>
       </c>
     </row>
@@ -693,21 +726,24 @@
         <v>REIT</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>360</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>370</v>
       </c>
-      <c r="F12">
-        <v>23</v>
-      </c>
       <c r="G12">
-        <v>2070</v>
-      </c>
-      <c r="H12" t="str">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
         <v>Office REIT</v>
       </c>
     </row>
@@ -719,21 +755,24 @@
         <v>InvIT</v>
       </c>
       <c r="C13">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>100</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>105</v>
       </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
       <c r="G13">
-        <v>1800</v>
-      </c>
-      <c r="H13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
         <v>Infrastructure</v>
       </c>
     </row>
@@ -745,21 +784,24 @@
         <v>InvIT</v>
       </c>
       <c r="C14">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>75</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>80</v>
       </c>
-      <c r="F14">
-        <v>7.5</v>
-      </c>
       <c r="G14">
-        <v>2025</v>
-      </c>
-      <c r="H14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
         <v>Infrastructure</v>
       </c>
     </row>
@@ -771,21 +813,24 @@
         <v>InvIT</v>
       </c>
       <c r="C15">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>160</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>165</v>
       </c>
-      <c r="F15">
-        <v>14</v>
-      </c>
       <c r="G15">
-        <v>2520</v>
-      </c>
-      <c r="H15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
         <v>Power Grid</v>
       </c>
     </row>
@@ -797,27 +842,30 @@
         <v>InvIT</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>108</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>112</v>
       </c>
-      <c r="F16">
-        <v>10.5</v>
-      </c>
       <c r="G16">
-        <v>1417.5</v>
-      </c>
-      <c r="H16" t="str">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
         <v>Power Grid</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
   </ignoredErrors>
 </worksheet>
 </file>